--- a/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
+++ b/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2bef4fc0c8172fbf/Desktop/Claude Cowork/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2002" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A3A22BF-07E4-4BD2-A4FA-FEEEC88AC57E}"/>
+  <xr:revisionPtr revIDLastSave="2044" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{037F7663-D939-47AC-95EF-9AE32040A36D}"/>
   <bookViews>
-    <workbookView xWindow="1155" yWindow="60" windowWidth="32055" windowHeight="20565" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
+    <workbookView xWindow="2970" yWindow="195" windowWidth="32055" windowHeight="20565" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -221,7 +221,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -249,12 +249,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -521,7 +515,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -601,7 +595,6 @@
     <xf numFmtId="164" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1068,7 +1061,7 @@
       <c r="A3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="31" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="3"/>
@@ -4781,7 +4774,7 @@
       <c r="N92" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="O92" s="34" t="s">
+      <c r="O92" s="33" t="s">
         <v>16</v>
       </c>
       <c r="P92" s="6" t="s">
@@ -4834,7 +4827,7 @@
       <c r="N93" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O93" s="33">
+      <c r="O93" s="32">
         <v>10</v>
       </c>
       <c r="P93" s="3" t="s">
@@ -4887,7 +4880,7 @@
       <c r="N94" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O94" s="33">
+      <c r="O94" s="32">
         <v>8</v>
       </c>
       <c r="P94" s="3" t="s">
@@ -4940,7 +4933,7 @@
       <c r="N95" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O95" s="33">
+      <c r="O95" s="32">
         <v>8</v>
       </c>
       <c r="P95" s="13" t="s">
@@ -4989,7 +4982,7 @@
       <c r="N96" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="O96" s="33">
+      <c r="O96" s="32">
         <v>8</v>
       </c>
       <c r="P96" s="3" t="s">
@@ -5040,7 +5033,7 @@
       <c r="N97" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="O97" s="35"/>
+      <c r="O97" s="34"/>
       <c r="P97" s="13" t="s">
         <v>12</v>
       </c>
@@ -5081,7 +5074,7 @@
         <v>40</v>
       </c>
       <c r="N98" s="28"/>
-      <c r="O98" s="36">
+      <c r="O98" s="35">
         <f>SUM(O93:O97)</f>
         <v>34</v>
       </c>
@@ -5120,7 +5113,7 @@
         <v>0</v>
       </c>
       <c r="N99" s="29"/>
-      <c r="O99" s="37">
+      <c r="O99" s="36">
         <v>0</v>
       </c>
       <c r="P99" s="29"/>
@@ -5157,7 +5150,7 @@
         <v>1</v>
       </c>
       <c r="N100" s="30"/>
-      <c r="O100" s="38">
+      <c r="O100" s="37">
         <v>0</v>
       </c>
       <c r="P100" s="30"/>
@@ -5331,10 +5324,10 @@
         <v>8</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C105" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>11</v>
@@ -5366,7 +5359,7 @@
       <c r="M105" s="9">
         <v>8</v>
       </c>
-      <c r="N105" s="13" t="s">
+      <c r="N105" s="39" t="s">
         <v>12</v>
       </c>
       <c r="O105" s="9"/>
@@ -5415,10 +5408,12 @@
       <c r="M106" s="9">
         <v>7</v>
       </c>
-      <c r="N106" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="O106" s="9"/>
+      <c r="N106" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="O106" s="9">
+        <v>8</v>
+      </c>
       <c r="P106" s="13" t="s">
         <v>12</v>
       </c>
@@ -5428,8 +5423,8 @@
       <c r="A107" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B107" s="3" t="s">
-        <v>11</v>
+      <c r="B107" s="27" t="s">
+        <v>32</v>
       </c>
       <c r="C107" s="13">
         <v>8</v>
@@ -5478,7 +5473,7 @@
       <c r="B108" s="23"/>
       <c r="C108" s="23">
         <f>SUM(C103:C107)</f>
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D108" s="23"/>
       <c r="E108" s="23">
@@ -5508,7 +5503,7 @@
       <c r="N108" s="28"/>
       <c r="O108" s="24">
         <f>SUM(O103:O107)</f>
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="P108" s="28"/>
       <c r="Q108" s="24">
@@ -5522,7 +5517,7 @@
       </c>
       <c r="B109" s="18"/>
       <c r="C109" s="18">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D109" s="18"/>
       <c r="E109" s="18">
@@ -5559,7 +5554,7 @@
       </c>
       <c r="B110" s="21"/>
       <c r="C110" s="21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D110" s="21"/>
       <c r="E110" s="21">
@@ -5632,7 +5627,7 @@
       <c r="M112" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="N112" s="39" t="s">
+      <c r="N112" s="38" t="s">
         <v>33</v>
       </c>
       <c r="O112" s="7" t="s">
@@ -5685,7 +5680,7 @@
       <c r="M113" s="9">
         <v>10</v>
       </c>
-      <c r="N113" s="40" t="s">
+      <c r="N113" s="39" t="s">
         <v>17</v>
       </c>
       <c r="O113" s="9">
@@ -5708,12 +5703,10 @@
       <c r="C114" s="3">
         <v>8</v>
       </c>
-      <c r="D114" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E114" s="3">
-        <v>8</v>
-      </c>
+      <c r="D114" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E114" s="3"/>
       <c r="F114" s="3" t="s">
         <v>11</v>
       </c>
@@ -5738,16 +5731,18 @@
       <c r="M114" s="9">
         <v>8</v>
       </c>
-      <c r="N114" s="40" t="s">
+      <c r="N114" s="39" t="s">
         <v>11</v>
       </c>
       <c r="O114" s="9">
         <v>8</v>
       </c>
-      <c r="P114" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q114" s="9"/>
+      <c r="P114" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q114" s="9">
+        <v>8</v>
+      </c>
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
@@ -5789,7 +5784,7 @@
       <c r="M115" s="9">
         <v>8</v>
       </c>
-      <c r="N115" s="41" t="s">
+      <c r="N115" s="40" t="s">
         <v>12</v>
       </c>
       <c r="O115" s="9"/>
@@ -5836,12 +5831,10 @@
       <c r="M116" s="9">
         <v>7</v>
       </c>
-      <c r="N116" s="40" t="s">
-        <v>11</v>
-      </c>
-      <c r="O116" s="9">
-        <v>8</v>
-      </c>
+      <c r="N116" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="O116" s="9"/>
       <c r="P116" s="13" t="s">
         <v>12</v>
       </c>
@@ -5885,7 +5878,7 @@
       <c r="M117" s="14">
         <v>7</v>
       </c>
-      <c r="N117" s="41" t="s">
+      <c r="N117" s="40" t="s">
         <v>12</v>
       </c>
       <c r="O117" s="14"/>
@@ -5906,7 +5899,7 @@
       <c r="D118" s="23"/>
       <c r="E118" s="23">
         <f>SUM(E113:E117)</f>
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="F118" s="23"/>
       <c r="G118" s="23">
@@ -5931,12 +5924,12 @@
       <c r="N118" s="28"/>
       <c r="O118" s="24">
         <f>SUM(O113:O117)</f>
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="P118" s="28"/>
       <c r="Q118" s="24">
         <f>SUM(Q113:Q117)</f>
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="119" spans="1:18" x14ac:dyDescent="0.25">
@@ -5949,7 +5942,7 @@
       </c>
       <c r="D119" s="18"/>
       <c r="E119" s="18">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="F119" s="18"/>
       <c r="G119" s="18">
@@ -5982,11 +5975,11 @@
       </c>
       <c r="B120" s="21"/>
       <c r="C120" s="21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D120" s="21"/>
       <c r="E120" s="21">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F120" s="21"/>
       <c r="G120" s="21">
@@ -6012,7 +6005,7 @@
       <c r="Q120" s="22">
         <v>0</v>
       </c>
-      <c r="R120" s="31"/>
+      <c r="R120" s="25"/>
     </row>
     <row r="121" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="122" spans="1:18" x14ac:dyDescent="0.25">
@@ -6143,12 +6136,10 @@
       <c r="G124" s="3">
         <v>8</v>
       </c>
-      <c r="H124" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I124" s="3">
-        <v>8</v>
-      </c>
+      <c r="H124" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I124" s="3"/>
       <c r="J124" s="3" t="s">
         <v>11</v>
       </c>
@@ -6167,10 +6158,12 @@
       <c r="O124" s="9">
         <v>8</v>
       </c>
-      <c r="P124" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q124" s="9"/>
+      <c r="P124" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q124" s="9">
+        <v>8</v>
+      </c>
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
@@ -6339,7 +6332,7 @@
       <c r="H128" s="23"/>
       <c r="I128" s="23">
         <f>SUM(I123:I127)</f>
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="J128" s="23"/>
       <c r="K128" s="23">
@@ -6359,7 +6352,7 @@
       <c r="P128" s="28"/>
       <c r="Q128" s="24">
         <f>SUM(Q123:Q127)</f>
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="129" spans="1:18" x14ac:dyDescent="0.25">
@@ -6380,7 +6373,7 @@
       </c>
       <c r="H129" s="18"/>
       <c r="I129" s="18">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="J129" s="18"/>
       <c r="K129" s="18">
@@ -6405,11 +6398,11 @@
       </c>
       <c r="B130" s="21"/>
       <c r="C130" s="21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D130" s="21"/>
       <c r="E130" s="21">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F130" s="21"/>
       <c r="G130" s="21">
@@ -6417,7 +6410,7 @@
       </c>
       <c r="H130" s="21"/>
       <c r="I130" s="21">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J130" s="21"/>
       <c r="K130" s="21">
@@ -6435,7 +6428,7 @@
       <c r="Q130" s="22">
         <v>0</v>
       </c>
-      <c r="R130" s="31"/>
+      <c r="R130" s="25"/>
     </row>
     <row r="131" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="132" spans="1:18" x14ac:dyDescent="0.25">
@@ -6478,7 +6471,7 @@
       <c r="M132" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="N132" s="39" t="s">
+      <c r="N132" s="38" t="s">
         <v>33</v>
       </c>
       <c r="O132" s="7" t="s">
@@ -6531,7 +6524,7 @@
       <c r="M133" s="9">
         <v>10</v>
       </c>
-      <c r="N133" s="40" t="s">
+      <c r="N133" s="39" t="s">
         <v>17</v>
       </c>
       <c r="O133" s="9">
@@ -6584,16 +6577,18 @@
       <c r="M134" s="9">
         <v>8</v>
       </c>
-      <c r="N134" s="40" t="s">
+      <c r="N134" s="39" t="s">
         <v>11</v>
       </c>
       <c r="O134" s="9">
         <v>8</v>
       </c>
-      <c r="P134" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q134" s="9"/>
+      <c r="P134" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q134" s="9">
+        <v>8</v>
+      </c>
     </row>
     <row r="135" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
@@ -6615,10 +6610,12 @@
       <c r="G135" s="3">
         <v>7</v>
       </c>
-      <c r="H135" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I135" s="3"/>
+      <c r="H135" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I135" s="3">
+        <v>8</v>
+      </c>
       <c r="J135" s="3" t="s">
         <v>11</v>
       </c>
@@ -6631,12 +6628,10 @@
       <c r="M135" s="9">
         <v>8</v>
       </c>
-      <c r="N135" s="40" t="s">
-        <v>11</v>
-      </c>
-      <c r="O135" s="9">
-        <v>8</v>
-      </c>
+      <c r="N135" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="O135" s="9"/>
       <c r="P135" s="13" t="s">
         <v>12</v>
       </c>
@@ -6680,12 +6675,10 @@
       <c r="M136" s="9">
         <v>7</v>
       </c>
-      <c r="N136" s="40" t="s">
-        <v>11</v>
-      </c>
-      <c r="O136" s="9">
-        <v>8</v>
-      </c>
+      <c r="N136" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="O136" s="9"/>
       <c r="P136" s="13" t="s">
         <v>12</v>
       </c>
@@ -6729,7 +6722,7 @@
       <c r="M137" s="14">
         <v>7</v>
       </c>
-      <c r="N137" s="41" t="s">
+      <c r="N137" s="40" t="s">
         <v>12</v>
       </c>
       <c r="O137" s="14"/>
@@ -6760,7 +6753,7 @@
       <c r="H138" s="23"/>
       <c r="I138" s="23">
         <f>SUM(I133:I137)</f>
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="J138" s="23"/>
       <c r="K138" s="23">
@@ -6775,12 +6768,12 @@
       <c r="N138" s="28"/>
       <c r="O138" s="24">
         <f>SUM(O133:O137)</f>
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="P138" s="28"/>
       <c r="Q138" s="24">
         <f>SUM(Q133:Q137)</f>
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="139" spans="1:18" x14ac:dyDescent="0.25">
@@ -6801,7 +6794,7 @@
       </c>
       <c r="H139" s="18"/>
       <c r="I139" s="18">
-        <v>-6</v>
+        <v>2</v>
       </c>
       <c r="J139" s="18"/>
       <c r="K139" s="18">
@@ -6826,11 +6819,11 @@
       </c>
       <c r="B140" s="21"/>
       <c r="C140" s="21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D140" s="21"/>
       <c r="E140" s="21">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="F140" s="21"/>
       <c r="G140" s="21">
@@ -6856,7 +6849,7 @@
       <c r="Q140" s="22">
         <v>0</v>
       </c>
-      <c r="R140" s="31"/>
+      <c r="R140" s="25"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
+++ b/SCHEMA KALASKUNGEN CLAUDE MASTER.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2bef4fc0c8172fbf/Desktop/Claude Cowork/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2044" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{037F7663-D939-47AC-95EF-9AE32040A36D}"/>
+  <xr:revisionPtr revIDLastSave="2302" documentId="13_ncr:1_{5A2AC64F-0607-4222-933F-ADAEE51C4F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC482332-9137-4F4F-BD5A-4C2FE05031FA}"/>
   <bookViews>
-    <workbookView xWindow="2970" yWindow="195" windowWidth="32055" windowHeight="20565" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
+    <workbookView xWindow="930" yWindow="90" windowWidth="21795" windowHeight="20790" xr2:uid="{DC0F372B-08EF-4BC4-9876-B81ECB143559}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1760" uniqueCount="63">
   <si>
     <t>Schema Kalaskungen</t>
   </si>
@@ -175,6 +175,60 @@
   <si>
     <t>Vecka 37 (7 sep-11 sep)</t>
   </si>
+  <si>
+    <t>07:00-11:45</t>
+  </si>
+  <si>
+    <t>Vecka 43 (19 okt-23 okt)</t>
+  </si>
+  <si>
+    <t>Vecka 44 (26 okt-30 okt)</t>
+  </si>
+  <si>
+    <t>Vecka 45 (2 nov-6 nov)</t>
+  </si>
+  <si>
+    <t>Vecka 46 (9 nov-13 nov)</t>
+  </si>
+  <si>
+    <t>Vecka 47 (16 nov-20 nov)</t>
+  </si>
+  <si>
+    <t>Vecka 48 (23 nov-27 nov)</t>
+  </si>
+  <si>
+    <t>Vecka 49 (30 nov-4 dec)</t>
+  </si>
+  <si>
+    <t>Vecka 50 (7 dec-11 dec)</t>
+  </si>
+  <si>
+    <t>Vecka 51 (14 dec-18 dec)</t>
+  </si>
+  <si>
+    <t>Vecka 52 (21 dec-25 dec)</t>
+  </si>
+  <si>
+    <t>Vecka 53 (28 dec-1 jan)</t>
+  </si>
+  <si>
+    <t>Vecka 1 (4 jan-8 jan)</t>
+  </si>
+  <si>
+    <t>Vecka 2 (11 jan-15 jan)</t>
+  </si>
+  <si>
+    <t>Emils sista dag</t>
+  </si>
+  <si>
+    <t>Alice sista dag</t>
+  </si>
+  <si>
+    <t>07:00-16:45 (VM)</t>
+  </si>
+  <si>
+    <t>07:00-15:45 (VM)</t>
+  </si>
 </sst>
 </file>
 
@@ -183,7 +237,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="\+0;\-0;0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -220,8 +274,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -249,6 +310,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -515,7 +582,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -625,6 +692,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -972,7 +1041,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R140"/>
+  <dimension ref="A1:R270"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -4951,27 +5020,27 @@
       <c r="C96" s="3">
         <v>8</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>11</v>
+      <c r="D96" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="E96" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F96" s="4" t="s">
         <v>12</v>
       </c>
       <c r="G96" s="3"/>
       <c r="H96" s="3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I96" s="3">
-        <v>8</v>
-      </c>
-      <c r="J96" s="3" t="s">
-        <v>34</v>
+        <v>7</v>
+      </c>
+      <c r="J96" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K96" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L96" s="3" t="s">
         <v>13</v>
@@ -5051,7 +5120,7 @@
       <c r="D98" s="23"/>
       <c r="E98" s="23">
         <f>SUM(E93:E97)</f>
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F98" s="23"/>
       <c r="G98" s="23">
@@ -5061,12 +5130,12 @@
       <c r="H98" s="23"/>
       <c r="I98" s="23">
         <f>SUM(I93:I97)</f>
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J98" s="23"/>
       <c r="K98" s="23">
         <f>SUM(K93:K97)</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L98" s="23"/>
       <c r="M98" s="24">
@@ -5094,7 +5163,7 @@
       </c>
       <c r="D99" s="18"/>
       <c r="E99" s="18">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="F99" s="18"/>
       <c r="G99" s="18">
@@ -5102,11 +5171,11 @@
       </c>
       <c r="H99" s="18"/>
       <c r="I99" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J99" s="18"/>
       <c r="K99" s="18">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L99" s="18"/>
       <c r="M99" s="19">
@@ -5131,7 +5200,7 @@
       </c>
       <c r="D100" s="21"/>
       <c r="E100" s="21">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F100" s="21"/>
       <c r="G100" s="21">
@@ -5143,7 +5212,7 @@
       </c>
       <c r="J100" s="21"/>
       <c r="K100" s="21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L100" s="21"/>
       <c r="M100" s="22">
@@ -5558,7 +5627,7 @@
       </c>
       <c r="D110" s="21"/>
       <c r="E110" s="21">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F110" s="21"/>
       <c r="G110" s="21">
@@ -5566,11 +5635,11 @@
       </c>
       <c r="H110" s="21"/>
       <c r="I110" s="21">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J110" s="21"/>
       <c r="K110" s="21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L110" s="21"/>
       <c r="M110" s="22">
@@ -5713,17 +5782,17 @@
       <c r="G114" s="3">
         <v>8</v>
       </c>
-      <c r="H114" s="3" t="s">
-        <v>11</v>
+      <c r="H114" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="I114" s="3">
-        <v>8</v>
-      </c>
-      <c r="J114" s="3" t="s">
-        <v>11</v>
+        <v>3.5</v>
+      </c>
+      <c r="J114" s="4" t="s">
+        <v>45</v>
       </c>
       <c r="K114" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L114" s="3" t="s">
         <v>11</v>
@@ -5909,12 +5978,12 @@
       <c r="H118" s="23"/>
       <c r="I118" s="23">
         <f>SUM(I113:I117)</f>
-        <v>42</v>
+        <v>37.5</v>
       </c>
       <c r="J118" s="23"/>
       <c r="K118" s="23">
         <f>SUM(K113:K117)</f>
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="L118" s="23"/>
       <c r="M118" s="24">
@@ -5950,11 +6019,11 @@
       </c>
       <c r="H119" s="18"/>
       <c r="I119" s="18">
-        <v>2</v>
+        <v>-2.5</v>
       </c>
       <c r="J119" s="18"/>
       <c r="K119" s="18">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L119" s="18"/>
       <c r="M119" s="19">
@@ -5979,7 +6048,7 @@
       </c>
       <c r="D120" s="21"/>
       <c r="E120" s="21">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F120" s="21"/>
       <c r="G120" s="21">
@@ -5987,11 +6056,11 @@
       </c>
       <c r="H120" s="21"/>
       <c r="I120" s="21">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J120" s="21"/>
       <c r="K120" s="21">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="L120" s="21"/>
       <c r="M120" s="22">
@@ -6402,7 +6471,7 @@
       </c>
       <c r="D130" s="21"/>
       <c r="E130" s="21">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F130" s="21"/>
       <c r="G130" s="21">
@@ -6410,11 +6479,11 @@
       </c>
       <c r="H130" s="21"/>
       <c r="I130" s="21">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J130" s="21"/>
       <c r="K130" s="21">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="L130" s="21"/>
       <c r="M130" s="22">
@@ -6716,8 +6785,8 @@
         <v>12</v>
       </c>
       <c r="K137" s="13"/>
-      <c r="L137" s="13" t="s">
-        <v>13</v>
+      <c r="L137" s="27" t="s">
+        <v>32</v>
       </c>
       <c r="M137" s="14">
         <v>7</v>
@@ -6823,7 +6892,7 @@
       </c>
       <c r="D140" s="21"/>
       <c r="E140" s="21">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="F140" s="21"/>
       <c r="G140" s="21">
@@ -6831,11 +6900,11 @@
       </c>
       <c r="H140" s="21"/>
       <c r="I140" s="21">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J140" s="21"/>
       <c r="K140" s="21">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="L140" s="21"/>
       <c r="M140" s="22">
@@ -6850,6 +6919,5524 @@
         <v>0</v>
       </c>
       <c r="R140" s="25"/>
+    </row>
+    <row r="141" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A142" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B142" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C142" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D142" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E142" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F142" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G142" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H142" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I142" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J142" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="K142" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L142" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="M142" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="N142" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="O142" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="P142" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q142" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A143" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C143" s="3">
+        <v>9</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E143" s="3">
+        <v>9</v>
+      </c>
+      <c r="F143" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G143" s="3">
+        <v>9</v>
+      </c>
+      <c r="H143" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I143" s="3">
+        <v>9</v>
+      </c>
+      <c r="J143" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K143" s="3">
+        <v>9</v>
+      </c>
+      <c r="L143" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="M143" s="9">
+        <v>9</v>
+      </c>
+      <c r="N143" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O143" s="9">
+        <v>9</v>
+      </c>
+      <c r="P143" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q143" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A144" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C144" s="3">
+        <v>8</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E144" s="3">
+        <v>8</v>
+      </c>
+      <c r="F144" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G144" s="3">
+        <v>7</v>
+      </c>
+      <c r="H144" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I144" s="3">
+        <v>8</v>
+      </c>
+      <c r="J144" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K144" s="3">
+        <v>8</v>
+      </c>
+      <c r="L144" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M144" s="9">
+        <v>8</v>
+      </c>
+      <c r="N144" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="O144" s="9">
+        <v>8</v>
+      </c>
+      <c r="P144" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q144" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A145" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C145" s="3">
+        <v>6</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E145" s="3">
+        <v>8</v>
+      </c>
+      <c r="F145" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G145" s="3">
+        <v>7</v>
+      </c>
+      <c r="H145" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I145" s="3">
+        <v>8</v>
+      </c>
+      <c r="J145" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K145" s="3">
+        <v>8</v>
+      </c>
+      <c r="L145" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M145" s="9">
+        <v>8</v>
+      </c>
+      <c r="N145" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="O145" s="9"/>
+      <c r="P145" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q145" s="9"/>
+    </row>
+    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A146" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C146" s="3">
+        <v>8</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E146" s="3">
+        <v>8</v>
+      </c>
+      <c r="F146" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G146" s="3">
+        <v>7</v>
+      </c>
+      <c r="H146" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I146" s="3">
+        <v>8</v>
+      </c>
+      <c r="J146" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K146" s="3">
+        <v>6</v>
+      </c>
+      <c r="L146" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M146" s="9">
+        <v>7</v>
+      </c>
+      <c r="N146" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="O146" s="9"/>
+      <c r="P146" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q146" s="9"/>
+    </row>
+    <row r="147" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A147" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C147" s="13">
+        <v>8</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E147" s="13">
+        <v>8</v>
+      </c>
+      <c r="F147" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G147" s="13">
+        <v>7</v>
+      </c>
+      <c r="H147" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I147" s="13">
+        <v>8</v>
+      </c>
+      <c r="J147" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="K147" s="13"/>
+      <c r="L147" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="M147" s="14">
+        <v>7</v>
+      </c>
+      <c r="N147" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="O147" s="14"/>
+      <c r="P147" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q147" s="14"/>
+    </row>
+    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A148" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B148" s="23"/>
+      <c r="C148" s="23">
+        <f>SUM(C143:C147)</f>
+        <v>39</v>
+      </c>
+      <c r="D148" s="23"/>
+      <c r="E148" s="23">
+        <v>40</v>
+      </c>
+      <c r="F148" s="23"/>
+      <c r="G148" s="23">
+        <f>SUM(G143:G147)</f>
+        <v>37</v>
+      </c>
+      <c r="H148" s="23"/>
+      <c r="I148" s="23">
+        <f>SUM(I143:I147)</f>
+        <v>41</v>
+      </c>
+      <c r="J148" s="23"/>
+      <c r="K148" s="23">
+        <f>SUM(K143:K147)</f>
+        <v>31</v>
+      </c>
+      <c r="L148" s="23"/>
+      <c r="M148" s="24">
+        <f>SUM(M143:M147)</f>
+        <v>39</v>
+      </c>
+      <c r="N148" s="28"/>
+      <c r="O148" s="24">
+        <f>SUM(O143:O147)</f>
+        <v>17</v>
+      </c>
+      <c r="P148" s="28"/>
+      <c r="Q148" s="24">
+        <f>SUM(Q143:Q147)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A149" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B149" s="18"/>
+      <c r="C149" s="18">
+        <v>-1</v>
+      </c>
+      <c r="D149" s="18"/>
+      <c r="E149" s="18">
+        <v>0</v>
+      </c>
+      <c r="F149" s="18"/>
+      <c r="G149" s="18">
+        <v>2</v>
+      </c>
+      <c r="H149" s="18"/>
+      <c r="I149" s="18">
+        <v>1</v>
+      </c>
+      <c r="J149" s="18"/>
+      <c r="K149" s="18">
+        <v>-1</v>
+      </c>
+      <c r="L149" s="18"/>
+      <c r="M149" s="19">
+        <v>-1</v>
+      </c>
+      <c r="N149" s="29"/>
+      <c r="O149" s="19">
+        <v>0</v>
+      </c>
+      <c r="P149" s="29"/>
+      <c r="Q149" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B150" s="21"/>
+      <c r="C150" s="21">
+        <v>2</v>
+      </c>
+      <c r="D150" s="21"/>
+      <c r="E150" s="21">
+        <v>-1</v>
+      </c>
+      <c r="F150" s="21"/>
+      <c r="G150" s="21">
+        <v>4</v>
+      </c>
+      <c r="H150" s="21"/>
+      <c r="I150" s="21">
+        <v>4</v>
+      </c>
+      <c r="J150" s="21"/>
+      <c r="K150" s="21">
+        <v>-2</v>
+      </c>
+      <c r="L150" s="21"/>
+      <c r="M150" s="22">
+        <v>0</v>
+      </c>
+      <c r="N150" s="30"/>
+      <c r="O150" s="22">
+        <v>0</v>
+      </c>
+      <c r="P150" s="30"/>
+      <c r="Q150" s="22">
+        <v>0</v>
+      </c>
+      <c r="R150" s="25"/>
+    </row>
+    <row r="151" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A152" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C152" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D152" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E152" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F152" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G152" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H152" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I152" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J152" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="K152" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L152" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="M152" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="N152" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="O152" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="P152" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q152" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A153" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C153" s="3">
+        <v>9</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E153" s="3">
+        <v>9</v>
+      </c>
+      <c r="F153" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G153" s="3">
+        <v>9</v>
+      </c>
+      <c r="H153" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I153" s="3">
+        <v>9</v>
+      </c>
+      <c r="J153" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K153" s="3">
+        <v>9</v>
+      </c>
+      <c r="L153" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="M153" s="9">
+        <v>9</v>
+      </c>
+      <c r="N153" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O153" s="9">
+        <v>9</v>
+      </c>
+      <c r="P153" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q153" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A154" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C154" s="3">
+        <v>8</v>
+      </c>
+      <c r="D154" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E154" s="3"/>
+      <c r="F154" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G154" s="3">
+        <v>7</v>
+      </c>
+      <c r="H154" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I154" s="3">
+        <v>8</v>
+      </c>
+      <c r="J154" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K154" s="3">
+        <v>8</v>
+      </c>
+      <c r="L154" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M154" s="9">
+        <v>8</v>
+      </c>
+      <c r="N154" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="O154" s="9">
+        <v>8</v>
+      </c>
+      <c r="P154" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q154" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A155" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C155" s="3">
+        <v>6</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E155" s="3">
+        <v>8</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G155" s="3">
+        <v>7</v>
+      </c>
+      <c r="H155" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I155" s="3">
+        <v>8</v>
+      </c>
+      <c r="J155" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K155" s="3">
+        <v>8</v>
+      </c>
+      <c r="L155" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M155" s="9">
+        <v>8</v>
+      </c>
+      <c r="N155" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="O155" s="9"/>
+      <c r="P155" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q155" s="9"/>
+    </row>
+    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A156" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C156" s="3">
+        <v>8</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E156" s="3">
+        <v>8</v>
+      </c>
+      <c r="F156" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G156" s="3"/>
+      <c r="H156" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I156" s="3">
+        <v>8</v>
+      </c>
+      <c r="J156" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K156" s="3">
+        <v>6</v>
+      </c>
+      <c r="L156" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M156" s="9">
+        <v>7</v>
+      </c>
+      <c r="N156" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="O156" s="9"/>
+      <c r="P156" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q156" s="9"/>
+    </row>
+    <row r="157" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A157" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C157" s="13">
+        <v>8</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E157" s="13">
+        <v>8</v>
+      </c>
+      <c r="F157" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G157" s="13">
+        <v>7</v>
+      </c>
+      <c r="H157" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I157" s="13">
+        <v>8</v>
+      </c>
+      <c r="J157" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="K157" s="13"/>
+      <c r="L157" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="M157" s="14">
+        <v>7</v>
+      </c>
+      <c r="N157" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="O157" s="14"/>
+      <c r="P157" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q157" s="14"/>
+    </row>
+    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A158" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B158" s="23"/>
+      <c r="C158" s="23">
+        <f>SUM(C153:C157)</f>
+        <v>39</v>
+      </c>
+      <c r="D158" s="23"/>
+      <c r="E158" s="23">
+        <f>SUM(E153:E157)</f>
+        <v>33</v>
+      </c>
+      <c r="F158" s="23"/>
+      <c r="G158" s="23">
+        <f>SUM(G153:G157)</f>
+        <v>30</v>
+      </c>
+      <c r="H158" s="23"/>
+      <c r="I158" s="23">
+        <f>SUM(I153:I157)</f>
+        <v>41</v>
+      </c>
+      <c r="J158" s="23"/>
+      <c r="K158" s="23">
+        <f>SUM(K153:K157)</f>
+        <v>31</v>
+      </c>
+      <c r="L158" s="23"/>
+      <c r="M158" s="24">
+        <f>SUM(M153:M157)</f>
+        <v>39</v>
+      </c>
+      <c r="N158" s="28"/>
+      <c r="O158" s="24">
+        <f>SUM(O153:O157)</f>
+        <v>17</v>
+      </c>
+      <c r="P158" s="28"/>
+      <c r="Q158" s="24">
+        <f>SUM(Q153:Q157)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A159" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B159" s="18"/>
+      <c r="C159" s="18">
+        <v>-1</v>
+      </c>
+      <c r="D159" s="18"/>
+      <c r="E159" s="18">
+        <v>-7</v>
+      </c>
+      <c r="F159" s="18"/>
+      <c r="G159" s="18">
+        <v>-5</v>
+      </c>
+      <c r="H159" s="18"/>
+      <c r="I159" s="18">
+        <v>1</v>
+      </c>
+      <c r="J159" s="18"/>
+      <c r="K159" s="18">
+        <v>-1</v>
+      </c>
+      <c r="L159" s="18"/>
+      <c r="M159" s="19">
+        <v>-1</v>
+      </c>
+      <c r="N159" s="29"/>
+      <c r="O159" s="19">
+        <v>0</v>
+      </c>
+      <c r="P159" s="29"/>
+      <c r="Q159" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A160" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B160" s="21"/>
+      <c r="C160" s="21">
+        <v>1</v>
+      </c>
+      <c r="D160" s="21"/>
+      <c r="E160" s="21">
+        <v>-8</v>
+      </c>
+      <c r="F160" s="21"/>
+      <c r="G160" s="21">
+        <v>-1</v>
+      </c>
+      <c r="H160" s="21"/>
+      <c r="I160" s="21">
+        <v>5</v>
+      </c>
+      <c r="J160" s="21"/>
+      <c r="K160" s="21">
+        <v>-3</v>
+      </c>
+      <c r="L160" s="21"/>
+      <c r="M160" s="22">
+        <v>-1</v>
+      </c>
+      <c r="N160" s="30"/>
+      <c r="O160" s="22">
+        <v>0</v>
+      </c>
+      <c r="P160" s="30"/>
+      <c r="Q160" s="22">
+        <v>0</v>
+      </c>
+      <c r="R160" s="25"/>
+    </row>
+    <row r="161" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A162" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B162" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C162" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D162" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E162" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F162" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G162" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H162" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I162" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J162" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="K162" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L162" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="M162" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="N162" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="O162" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="P162" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q162" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A163" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C163" s="3">
+        <v>9</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E163" s="3">
+        <v>9</v>
+      </c>
+      <c r="F163" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G163" s="3">
+        <v>9</v>
+      </c>
+      <c r="H163" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I163" s="3">
+        <v>9</v>
+      </c>
+      <c r="J163" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K163" s="3">
+        <v>9</v>
+      </c>
+      <c r="L163" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="M163" s="9">
+        <v>9</v>
+      </c>
+      <c r="N163" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O163" s="9">
+        <v>9</v>
+      </c>
+      <c r="P163" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q163" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A164" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C164" s="3">
+        <v>8</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E164" s="3">
+        <v>8</v>
+      </c>
+      <c r="F164" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G164" s="3">
+        <v>7</v>
+      </c>
+      <c r="H164" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I164" s="3">
+        <v>8</v>
+      </c>
+      <c r="J164" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K164" s="3">
+        <v>8</v>
+      </c>
+      <c r="L164" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="M164" s="9">
+        <v>8</v>
+      </c>
+      <c r="N164" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="O164" s="9">
+        <v>8</v>
+      </c>
+      <c r="P164" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q164" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A165" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C165" s="3">
+        <v>6</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E165" s="3">
+        <v>8</v>
+      </c>
+      <c r="F165" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G165" s="3">
+        <v>7</v>
+      </c>
+      <c r="H165" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I165" s="3">
+        <v>8</v>
+      </c>
+      <c r="J165" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K165" s="3">
+        <v>8</v>
+      </c>
+      <c r="L165" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M165" s="9">
+        <v>8</v>
+      </c>
+      <c r="N165" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="O165" s="9"/>
+      <c r="P165" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q165" s="9"/>
+    </row>
+    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A166" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C166" s="3">
+        <v>8</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E166" s="3">
+        <v>8</v>
+      </c>
+      <c r="F166" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G166" s="3">
+        <v>7</v>
+      </c>
+      <c r="H166" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I166" s="3">
+        <v>8</v>
+      </c>
+      <c r="J166" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K166" s="3">
+        <v>6</v>
+      </c>
+      <c r="L166" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M166" s="9">
+        <v>7</v>
+      </c>
+      <c r="N166" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="O166" s="9"/>
+      <c r="P166" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q166" s="9"/>
+    </row>
+    <row r="167" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A167" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C167" s="13">
+        <v>8</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E167" s="13">
+        <v>8</v>
+      </c>
+      <c r="F167" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G167" s="13">
+        <v>7</v>
+      </c>
+      <c r="H167" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I167" s="13">
+        <v>8</v>
+      </c>
+      <c r="J167" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="K167" s="13"/>
+      <c r="L167" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="M167" s="14">
+        <v>7</v>
+      </c>
+      <c r="N167" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="O167" s="14"/>
+      <c r="P167" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q167" s="14"/>
+    </row>
+    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A168" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B168" s="23"/>
+      <c r="C168" s="23">
+        <f>SUM(C163:C167)</f>
+        <v>39</v>
+      </c>
+      <c r="D168" s="23"/>
+      <c r="E168" s="23">
+        <f>SUM(E163:E167)</f>
+        <v>41</v>
+      </c>
+      <c r="F168" s="23"/>
+      <c r="G168" s="23">
+        <f>SUM(G163:G167)</f>
+        <v>37</v>
+      </c>
+      <c r="H168" s="23"/>
+      <c r="I168" s="23">
+        <f>SUM(I163:I167)</f>
+        <v>41</v>
+      </c>
+      <c r="J168" s="23"/>
+      <c r="K168" s="23">
+        <f>SUM(K163:K167)</f>
+        <v>31</v>
+      </c>
+      <c r="L168" s="23"/>
+      <c r="M168" s="24">
+        <f>SUM(M163:M167)</f>
+        <v>39</v>
+      </c>
+      <c r="N168" s="28"/>
+      <c r="O168" s="24">
+        <f>SUM(O163:O167)</f>
+        <v>17</v>
+      </c>
+      <c r="P168" s="28"/>
+      <c r="Q168" s="24">
+        <f>SUM(Q163:Q167)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A169" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B169" s="18"/>
+      <c r="C169" s="18">
+        <v>-1</v>
+      </c>
+      <c r="D169" s="18"/>
+      <c r="E169" s="18">
+        <v>1</v>
+      </c>
+      <c r="F169" s="18"/>
+      <c r="G169" s="18">
+        <v>2</v>
+      </c>
+      <c r="H169" s="18"/>
+      <c r="I169" s="18">
+        <v>1</v>
+      </c>
+      <c r="J169" s="18"/>
+      <c r="K169" s="18">
+        <v>-1</v>
+      </c>
+      <c r="L169" s="18"/>
+      <c r="M169" s="19">
+        <v>-1</v>
+      </c>
+      <c r="N169" s="29"/>
+      <c r="O169" s="19">
+        <v>0</v>
+      </c>
+      <c r="P169" s="29"/>
+      <c r="Q169" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A170" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B170" s="21"/>
+      <c r="C170" s="21">
+        <v>0</v>
+      </c>
+      <c r="D170" s="21"/>
+      <c r="E170" s="21">
+        <v>-7</v>
+      </c>
+      <c r="F170" s="21"/>
+      <c r="G170" s="21">
+        <v>1</v>
+      </c>
+      <c r="H170" s="21"/>
+      <c r="I170" s="21">
+        <v>6</v>
+      </c>
+      <c r="J170" s="21"/>
+      <c r="K170" s="21">
+        <v>-4</v>
+      </c>
+      <c r="L170" s="21"/>
+      <c r="M170" s="22">
+        <v>1</v>
+      </c>
+      <c r="N170" s="30"/>
+      <c r="O170" s="22">
+        <v>0</v>
+      </c>
+      <c r="P170" s="30"/>
+      <c r="Q170" s="22">
+        <v>0</v>
+      </c>
+      <c r="R170" s="25"/>
+    </row>
+    <row r="171" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A172" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B172" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D172" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E172" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F172" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G172" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H172" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I172" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J172" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="K172" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L172" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="M172" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="N172" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="O172" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="P172" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q172" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A173" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C173" s="3">
+        <v>8</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E173" s="3">
+        <v>8</v>
+      </c>
+      <c r="F173" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G173" s="3">
+        <v>7</v>
+      </c>
+      <c r="H173" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I173" s="3">
+        <v>8</v>
+      </c>
+      <c r="J173" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K173" s="3">
+        <v>8</v>
+      </c>
+      <c r="L173" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M173" s="9">
+        <v>8</v>
+      </c>
+      <c r="N173" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="O173" s="9">
+        <v>8</v>
+      </c>
+      <c r="P173" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q173" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A174" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C174" s="3">
+        <v>8</v>
+      </c>
+      <c r="D174" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E174" s="3">
+        <v>8</v>
+      </c>
+      <c r="F174" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G174" s="3">
+        <v>7</v>
+      </c>
+      <c r="H174" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I174" s="3">
+        <v>8</v>
+      </c>
+      <c r="J174" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K174" s="3">
+        <v>8</v>
+      </c>
+      <c r="L174" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M174" s="9">
+        <v>8</v>
+      </c>
+      <c r="N174" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="O174" s="9">
+        <v>8</v>
+      </c>
+      <c r="P174" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q174" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A175" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C175" s="3">
+        <v>8</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E175" s="3">
+        <v>8</v>
+      </c>
+      <c r="F175" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G175" s="3">
+        <v>7</v>
+      </c>
+      <c r="H175" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I175" s="3">
+        <v>8</v>
+      </c>
+      <c r="J175" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K175" s="3">
+        <v>8</v>
+      </c>
+      <c r="L175" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M175" s="9">
+        <v>8</v>
+      </c>
+      <c r="N175" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="O175" s="9"/>
+      <c r="P175" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q175" s="9"/>
+    </row>
+    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A176" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C176" s="3">
+        <v>8</v>
+      </c>
+      <c r="D176" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E176" s="3">
+        <v>8</v>
+      </c>
+      <c r="F176" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G176" s="3">
+        <v>7</v>
+      </c>
+      <c r="H176" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I176" s="3">
+        <v>8</v>
+      </c>
+      <c r="J176" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K176" s="3">
+        <v>8</v>
+      </c>
+      <c r="L176" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M176" s="9">
+        <v>7</v>
+      </c>
+      <c r="N176" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="O176" s="9"/>
+      <c r="P176" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q176" s="9"/>
+    </row>
+    <row r="177" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A177" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C177" s="13">
+        <v>8</v>
+      </c>
+      <c r="D177" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E177" s="13">
+        <v>8</v>
+      </c>
+      <c r="F177" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G177" s="13">
+        <v>7</v>
+      </c>
+      <c r="H177" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I177" s="13">
+        <v>8</v>
+      </c>
+      <c r="J177" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="K177" s="13"/>
+      <c r="L177" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="M177" s="14">
+        <v>7</v>
+      </c>
+      <c r="N177" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="O177" s="14"/>
+      <c r="P177" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q177" s="14"/>
+    </row>
+    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A178" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B178" s="23"/>
+      <c r="C178" s="23">
+        <f>SUM(C173:C177)</f>
+        <v>40</v>
+      </c>
+      <c r="D178" s="23"/>
+      <c r="E178" s="23">
+        <f>SUM(E173:E177)</f>
+        <v>40</v>
+      </c>
+      <c r="F178" s="23"/>
+      <c r="G178" s="23">
+        <f>SUM(G173:G177)</f>
+        <v>35</v>
+      </c>
+      <c r="H178" s="23"/>
+      <c r="I178" s="23">
+        <f>SUM(I173:I177)</f>
+        <v>40</v>
+      </c>
+      <c r="J178" s="23"/>
+      <c r="K178" s="23">
+        <f>SUM(K173:K177)</f>
+        <v>32</v>
+      </c>
+      <c r="L178" s="23"/>
+      <c r="M178" s="24">
+        <f>SUM(M173:M177)</f>
+        <v>38</v>
+      </c>
+      <c r="N178" s="28"/>
+      <c r="O178" s="24">
+        <f>SUM(O173:O177)</f>
+        <v>16</v>
+      </c>
+      <c r="P178" s="28"/>
+      <c r="Q178" s="24">
+        <f>SUM(Q173:Q177)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A179" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B179" s="18"/>
+      <c r="C179" s="18">
+        <v>0</v>
+      </c>
+      <c r="D179" s="18"/>
+      <c r="E179" s="18">
+        <v>0</v>
+      </c>
+      <c r="F179" s="18"/>
+      <c r="G179" s="18">
+        <v>0</v>
+      </c>
+      <c r="H179" s="18"/>
+      <c r="I179" s="18">
+        <v>0</v>
+      </c>
+      <c r="J179" s="18"/>
+      <c r="K179" s="18">
+        <v>0</v>
+      </c>
+      <c r="L179" s="18"/>
+      <c r="M179" s="19">
+        <v>-2</v>
+      </c>
+      <c r="N179" s="29"/>
+      <c r="O179" s="19">
+        <v>0</v>
+      </c>
+      <c r="P179" s="29"/>
+      <c r="Q179" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A180" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B180" s="21"/>
+      <c r="C180" s="21">
+        <v>0</v>
+      </c>
+      <c r="D180" s="21"/>
+      <c r="E180" s="21">
+        <v>-7</v>
+      </c>
+      <c r="F180" s="21"/>
+      <c r="G180" s="21">
+        <v>1</v>
+      </c>
+      <c r="H180" s="21"/>
+      <c r="I180" s="21">
+        <v>6</v>
+      </c>
+      <c r="J180" s="21"/>
+      <c r="K180" s="21">
+        <v>-4</v>
+      </c>
+      <c r="L180" s="21"/>
+      <c r="M180" s="22">
+        <v>-1</v>
+      </c>
+      <c r="N180" s="30"/>
+      <c r="O180" s="22">
+        <v>0</v>
+      </c>
+      <c r="P180" s="30"/>
+      <c r="Q180" s="22">
+        <v>0</v>
+      </c>
+      <c r="R180" s="25"/>
+    </row>
+    <row r="181" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A182" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B182" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C182" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D182" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E182" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F182" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G182" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H182" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I182" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J182" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="K182" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L182" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="M182" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="N182" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="O182" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="P182" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q182" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A183" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C183" s="3">
+        <v>10</v>
+      </c>
+      <c r="D183" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E183" s="3">
+        <v>10</v>
+      </c>
+      <c r="F183" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G183" s="3">
+        <v>10</v>
+      </c>
+      <c r="H183" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I183" s="3">
+        <v>10</v>
+      </c>
+      <c r="J183" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K183" s="3">
+        <v>10</v>
+      </c>
+      <c r="L183" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M183" s="9">
+        <v>10</v>
+      </c>
+      <c r="N183" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="O183" s="9">
+        <v>10</v>
+      </c>
+      <c r="P183" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q183" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A184" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C184" s="3">
+        <v>8</v>
+      </c>
+      <c r="D184" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E184" s="3">
+        <v>8</v>
+      </c>
+      <c r="F184" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G184" s="3">
+        <v>8</v>
+      </c>
+      <c r="H184" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I184" s="3">
+        <v>8</v>
+      </c>
+      <c r="J184" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K184" s="3">
+        <v>8</v>
+      </c>
+      <c r="L184" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M184" s="9">
+        <v>8</v>
+      </c>
+      <c r="N184" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="O184" s="9">
+        <v>8</v>
+      </c>
+      <c r="P184" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q184" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A185" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C185" s="3">
+        <v>6</v>
+      </c>
+      <c r="D185" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E185" s="3">
+        <v>8</v>
+      </c>
+      <c r="F185" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G185" s="3">
+        <v>7</v>
+      </c>
+      <c r="H185" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I185" s="3">
+        <v>8</v>
+      </c>
+      <c r="J185" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K185" s="3">
+        <v>8</v>
+      </c>
+      <c r="L185" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M185" s="9">
+        <v>8</v>
+      </c>
+      <c r="N185" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="O185" s="9"/>
+      <c r="P185" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q185" s="9"/>
+    </row>
+    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A186" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C186" s="3">
+        <v>8</v>
+      </c>
+      <c r="D186" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E186" s="3">
+        <v>8</v>
+      </c>
+      <c r="F186" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G186" s="3">
+        <v>7</v>
+      </c>
+      <c r="H186" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I186" s="3">
+        <v>8</v>
+      </c>
+      <c r="J186" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K186" s="3">
+        <v>6</v>
+      </c>
+      <c r="L186" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M186" s="9">
+        <v>7</v>
+      </c>
+      <c r="N186" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="O186" s="9"/>
+      <c r="P186" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q186" s="9"/>
+    </row>
+    <row r="187" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A187" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C187" s="13">
+        <v>8</v>
+      </c>
+      <c r="D187" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E187" s="13">
+        <v>8</v>
+      </c>
+      <c r="F187" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G187" s="13">
+        <v>7</v>
+      </c>
+      <c r="H187" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I187" s="13">
+        <v>8</v>
+      </c>
+      <c r="J187" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="K187" s="13"/>
+      <c r="L187" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="M187" s="14">
+        <v>7</v>
+      </c>
+      <c r="N187" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="O187" s="14"/>
+      <c r="P187" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q187" s="14"/>
+    </row>
+    <row r="188" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A188" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B188" s="23"/>
+      <c r="C188" s="23">
+        <f>SUM(C183:C187)</f>
+        <v>40</v>
+      </c>
+      <c r="D188" s="23"/>
+      <c r="E188" s="23">
+        <f>SUM(E183:E187)</f>
+        <v>42</v>
+      </c>
+      <c r="F188" s="23"/>
+      <c r="G188" s="23">
+        <f>SUM(G183:G187)</f>
+        <v>39</v>
+      </c>
+      <c r="H188" s="23"/>
+      <c r="I188" s="23">
+        <f>SUM(I183:I187)</f>
+        <v>42</v>
+      </c>
+      <c r="J188" s="23"/>
+      <c r="K188" s="23">
+        <f>SUM(K183:K187)</f>
+        <v>32</v>
+      </c>
+      <c r="L188" s="23"/>
+      <c r="M188" s="24">
+        <f>SUM(M183:M187)</f>
+        <v>40</v>
+      </c>
+      <c r="N188" s="28"/>
+      <c r="O188" s="24">
+        <f>SUM(O183:O187)</f>
+        <v>18</v>
+      </c>
+      <c r="P188" s="28"/>
+      <c r="Q188" s="24">
+        <f>SUM(Q183:Q187)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A189" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B189" s="18"/>
+      <c r="C189" s="18">
+        <v>0</v>
+      </c>
+      <c r="D189" s="18"/>
+      <c r="E189" s="18">
+        <v>-6</v>
+      </c>
+      <c r="F189" s="18"/>
+      <c r="G189" s="18">
+        <v>-3</v>
+      </c>
+      <c r="H189" s="18"/>
+      <c r="I189" s="18">
+        <v>2</v>
+      </c>
+      <c r="J189" s="18"/>
+      <c r="K189" s="18">
+        <v>0</v>
+      </c>
+      <c r="L189" s="18"/>
+      <c r="M189" s="19">
+        <v>0</v>
+      </c>
+      <c r="N189" s="29"/>
+      <c r="O189" s="19">
+        <v>0</v>
+      </c>
+      <c r="P189" s="29"/>
+      <c r="Q189" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A190" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B190" s="21"/>
+      <c r="C190" s="21">
+        <v>3</v>
+      </c>
+      <c r="D190" s="21"/>
+      <c r="E190" s="21">
+        <v>-1</v>
+      </c>
+      <c r="F190" s="21"/>
+      <c r="G190" s="21">
+        <v>2</v>
+      </c>
+      <c r="H190" s="21"/>
+      <c r="I190" s="21">
+        <v>3</v>
+      </c>
+      <c r="J190" s="21"/>
+      <c r="K190" s="21">
+        <v>-1</v>
+      </c>
+      <c r="L190" s="21"/>
+      <c r="M190" s="22">
+        <v>1</v>
+      </c>
+      <c r="N190" s="30"/>
+      <c r="O190" s="22">
+        <v>0</v>
+      </c>
+      <c r="P190" s="30"/>
+      <c r="Q190" s="22">
+        <v>0</v>
+      </c>
+      <c r="R190" s="41"/>
+    </row>
+    <row r="191" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="192" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A192" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B192" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C192" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D192" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E192" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F192" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G192" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H192" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I192" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J192" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="K192" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L192" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="M192" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="N192" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="O192" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="P192" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q192" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="193" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A193" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C193" s="3">
+        <v>10</v>
+      </c>
+      <c r="D193" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E193" s="3">
+        <v>10</v>
+      </c>
+      <c r="F193" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G193" s="3">
+        <v>10</v>
+      </c>
+      <c r="H193" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I193" s="3">
+        <v>10</v>
+      </c>
+      <c r="J193" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K193" s="3">
+        <v>10</v>
+      </c>
+      <c r="L193" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M193" s="9">
+        <v>10</v>
+      </c>
+      <c r="N193" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="O193" s="9">
+        <v>10</v>
+      </c>
+      <c r="P193" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q193" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="194" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A194" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C194" s="3">
+        <v>8</v>
+      </c>
+      <c r="D194" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E194" s="3">
+        <v>8</v>
+      </c>
+      <c r="F194" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G194" s="3">
+        <v>8</v>
+      </c>
+      <c r="H194" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I194" s="3">
+        <v>8</v>
+      </c>
+      <c r="J194" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K194" s="3">
+        <v>8</v>
+      </c>
+      <c r="L194" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M194" s="9">
+        <v>8</v>
+      </c>
+      <c r="N194" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="O194" s="9">
+        <v>8</v>
+      </c>
+      <c r="P194" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q194" s="9">
+        <v>8</v>
+      </c>
+      <c r="R194" s="42" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="195" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A195" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B195" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C195" s="3">
+        <v>6</v>
+      </c>
+      <c r="D195" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E195" s="3">
+        <v>8</v>
+      </c>
+      <c r="F195" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G195" s="3">
+        <v>7</v>
+      </c>
+      <c r="H195" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I195" s="3">
+        <v>8</v>
+      </c>
+      <c r="J195" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K195" s="3">
+        <v>8</v>
+      </c>
+      <c r="L195" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M195" s="9">
+        <v>8</v>
+      </c>
+      <c r="N195" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="O195" s="9"/>
+      <c r="P195" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q195" s="9"/>
+    </row>
+    <row r="196" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A196" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B196" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C196" s="3">
+        <v>8</v>
+      </c>
+      <c r="D196" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E196" s="3">
+        <v>8</v>
+      </c>
+      <c r="F196" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G196" s="3"/>
+      <c r="H196" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I196" s="3">
+        <v>8</v>
+      </c>
+      <c r="J196" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K196" s="3">
+        <v>6</v>
+      </c>
+      <c r="L196" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M196" s="9">
+        <v>7</v>
+      </c>
+      <c r="N196" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="O196" s="9"/>
+      <c r="P196" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q196" s="9"/>
+    </row>
+    <row r="197" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A197" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B197" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C197" s="13">
+        <v>8</v>
+      </c>
+      <c r="D197" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E197" s="13">
+        <v>8</v>
+      </c>
+      <c r="F197" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G197" s="13">
+        <v>7</v>
+      </c>
+      <c r="H197" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I197" s="13">
+        <v>8</v>
+      </c>
+      <c r="J197" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="K197" s="13"/>
+      <c r="L197" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="M197" s="14">
+        <v>7</v>
+      </c>
+      <c r="N197" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="O197" s="14"/>
+      <c r="P197" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q197" s="14"/>
+    </row>
+    <row r="198" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A198" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B198" s="23"/>
+      <c r="C198" s="23">
+        <f>SUM(C193:C197)</f>
+        <v>40</v>
+      </c>
+      <c r="D198" s="23"/>
+      <c r="E198" s="23">
+        <f>SUM(E193:E197)</f>
+        <v>42</v>
+      </c>
+      <c r="F198" s="23"/>
+      <c r="G198" s="23">
+        <f>SUM(G193:G197)</f>
+        <v>32</v>
+      </c>
+      <c r="H198" s="23"/>
+      <c r="I198" s="23">
+        <f>SUM(I193:I197)</f>
+        <v>42</v>
+      </c>
+      <c r="J198" s="23"/>
+      <c r="K198" s="23">
+        <f>SUM(K193:K197)</f>
+        <v>32</v>
+      </c>
+      <c r="L198" s="23"/>
+      <c r="M198" s="24">
+        <f>SUM(M193:M197)</f>
+        <v>40</v>
+      </c>
+      <c r="N198" s="28"/>
+      <c r="O198" s="24">
+        <f>SUM(O193:O197)</f>
+        <v>18</v>
+      </c>
+      <c r="P198" s="28"/>
+      <c r="Q198" s="24">
+        <f>SUM(Q193:Q197)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="199" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A199" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B199" s="18"/>
+      <c r="C199" s="18">
+        <v>0</v>
+      </c>
+      <c r="D199" s="18"/>
+      <c r="E199" s="18">
+        <v>-6</v>
+      </c>
+      <c r="F199" s="18"/>
+      <c r="G199" s="18">
+        <v>-3</v>
+      </c>
+      <c r="H199" s="18"/>
+      <c r="I199" s="18">
+        <v>2</v>
+      </c>
+      <c r="J199" s="18"/>
+      <c r="K199" s="18">
+        <v>0</v>
+      </c>
+      <c r="L199" s="18"/>
+      <c r="M199" s="19">
+        <v>0</v>
+      </c>
+      <c r="N199" s="29"/>
+      <c r="O199" s="19">
+        <v>0</v>
+      </c>
+      <c r="P199" s="29"/>
+      <c r="Q199" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A200" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B200" s="21"/>
+      <c r="C200" s="21">
+        <v>3</v>
+      </c>
+      <c r="D200" s="21"/>
+      <c r="E200" s="21">
+        <v>-1</v>
+      </c>
+      <c r="F200" s="21"/>
+      <c r="G200" s="21">
+        <v>2</v>
+      </c>
+      <c r="H200" s="21"/>
+      <c r="I200" s="21">
+        <v>3</v>
+      </c>
+      <c r="J200" s="21"/>
+      <c r="K200" s="21">
+        <v>-1</v>
+      </c>
+      <c r="L200" s="21"/>
+      <c r="M200" s="22">
+        <v>1</v>
+      </c>
+      <c r="N200" s="30"/>
+      <c r="O200" s="22">
+        <v>0</v>
+      </c>
+      <c r="P200" s="30"/>
+      <c r="Q200" s="22">
+        <v>0</v>
+      </c>
+      <c r="R200" s="41"/>
+    </row>
+    <row r="201" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="202" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A202" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B202" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C202" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D202" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E202" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F202" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G202" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H202" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I202" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J202" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="K202" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L202" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="M202" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="N202" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="O202" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="P202" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q202" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="203" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A203" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B203" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C203" s="3">
+        <v>10</v>
+      </c>
+      <c r="D203" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E203" s="3">
+        <v>10</v>
+      </c>
+      <c r="F203" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="G203" s="3">
+        <v>10</v>
+      </c>
+      <c r="H203" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I203" s="3">
+        <v>10</v>
+      </c>
+      <c r="J203" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K203" s="3">
+        <v>10</v>
+      </c>
+      <c r="L203" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M203" s="9">
+        <v>10</v>
+      </c>
+      <c r="N203" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="O203" s="9">
+        <v>10</v>
+      </c>
+      <c r="P203" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q203" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="204" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A204" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B204" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C204" s="3">
+        <v>8</v>
+      </c>
+      <c r="D204" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E204" s="3">
+        <v>8</v>
+      </c>
+      <c r="F204" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="G204" s="3">
+        <v>8</v>
+      </c>
+      <c r="H204" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I204" s="3">
+        <v>8</v>
+      </c>
+      <c r="J204" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K204" s="3">
+        <v>8</v>
+      </c>
+      <c r="L204" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M204" s="9">
+        <v>8</v>
+      </c>
+      <c r="N204" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="O204" s="9">
+        <v>8</v>
+      </c>
+      <c r="P204" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q204" s="9">
+        <v>8</v>
+      </c>
+      <c r="R204" s="42" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="205" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A205" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B205" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C205" s="3">
+        <v>6</v>
+      </c>
+      <c r="D205" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E205" s="3">
+        <v>8</v>
+      </c>
+      <c r="F205" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="G205" s="3">
+        <v>7</v>
+      </c>
+      <c r="H205" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I205" s="3">
+        <v>8</v>
+      </c>
+      <c r="J205" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K205" s="3">
+        <v>8</v>
+      </c>
+      <c r="L205" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M205" s="9">
+        <v>8</v>
+      </c>
+      <c r="N205" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="O205" s="9"/>
+      <c r="P205" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q205" s="9"/>
+    </row>
+    <row r="206" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A206" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B206" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C206" s="3">
+        <v>8</v>
+      </c>
+      <c r="D206" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E206" s="3">
+        <v>8</v>
+      </c>
+      <c r="F206" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="G206" s="3">
+        <v>7</v>
+      </c>
+      <c r="H206" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I206" s="3">
+        <v>8</v>
+      </c>
+      <c r="J206" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K206" s="3">
+        <v>6</v>
+      </c>
+      <c r="L206" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M206" s="9">
+        <v>7</v>
+      </c>
+      <c r="N206" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="O206" s="9"/>
+      <c r="P206" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q206" s="9"/>
+    </row>
+    <row r="207" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A207" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B207" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C207" s="13">
+        <v>8</v>
+      </c>
+      <c r="D207" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E207" s="13">
+        <v>8</v>
+      </c>
+      <c r="F207" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="G207" s="13">
+        <v>7</v>
+      </c>
+      <c r="H207" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I207" s="13">
+        <v>8</v>
+      </c>
+      <c r="J207" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="K207" s="13"/>
+      <c r="L207" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="M207" s="14">
+        <v>7</v>
+      </c>
+      <c r="N207" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="O207" s="14"/>
+      <c r="P207" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q207" s="14"/>
+    </row>
+    <row r="208" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A208" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B208" s="23"/>
+      <c r="C208" s="23">
+        <f>SUM(C203:C207)</f>
+        <v>40</v>
+      </c>
+      <c r="D208" s="23"/>
+      <c r="E208" s="23">
+        <f>SUM(E203:E207)</f>
+        <v>42</v>
+      </c>
+      <c r="F208" s="23"/>
+      <c r="G208" s="23">
+        <f>SUM(G203:G207)</f>
+        <v>39</v>
+      </c>
+      <c r="H208" s="23"/>
+      <c r="I208" s="23">
+        <f>SUM(I203:I207)</f>
+        <v>42</v>
+      </c>
+      <c r="J208" s="23"/>
+      <c r="K208" s="23">
+        <f>SUM(K203:K207)</f>
+        <v>32</v>
+      </c>
+      <c r="L208" s="23"/>
+      <c r="M208" s="24">
+        <f>SUM(M203:M207)</f>
+        <v>40</v>
+      </c>
+      <c r="N208" s="28"/>
+      <c r="O208" s="24">
+        <f>SUM(O203:O207)</f>
+        <v>18</v>
+      </c>
+      <c r="P208" s="28"/>
+      <c r="Q208" s="24">
+        <f>SUM(Q203:Q207)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="209" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A209" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B209" s="18"/>
+      <c r="C209" s="18">
+        <v>0</v>
+      </c>
+      <c r="D209" s="18"/>
+      <c r="E209" s="18">
+        <v>-6</v>
+      </c>
+      <c r="F209" s="18"/>
+      <c r="G209" s="18">
+        <v>-3</v>
+      </c>
+      <c r="H209" s="18"/>
+      <c r="I209" s="18">
+        <v>2</v>
+      </c>
+      <c r="J209" s="18"/>
+      <c r="K209" s="18">
+        <v>0</v>
+      </c>
+      <c r="L209" s="18"/>
+      <c r="M209" s="19">
+        <v>0</v>
+      </c>
+      <c r="N209" s="29"/>
+      <c r="O209" s="19">
+        <v>0</v>
+      </c>
+      <c r="P209" s="29"/>
+      <c r="Q209" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A210" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B210" s="21"/>
+      <c r="C210" s="21">
+        <v>3</v>
+      </c>
+      <c r="D210" s="21"/>
+      <c r="E210" s="21">
+        <v>-1</v>
+      </c>
+      <c r="F210" s="21"/>
+      <c r="G210" s="21">
+        <v>2</v>
+      </c>
+      <c r="H210" s="21"/>
+      <c r="I210" s="21">
+        <v>3</v>
+      </c>
+      <c r="J210" s="21"/>
+      <c r="K210" s="21">
+        <v>-1</v>
+      </c>
+      <c r="L210" s="21"/>
+      <c r="M210" s="22">
+        <v>1</v>
+      </c>
+      <c r="N210" s="30"/>
+      <c r="O210" s="22">
+        <v>0</v>
+      </c>
+      <c r="P210" s="30"/>
+      <c r="Q210" s="22">
+        <v>0</v>
+      </c>
+      <c r="R210" s="41"/>
+    </row>
+    <row r="211" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="212" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A212" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B212" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C212" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D212" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E212" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F212" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G212" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H212" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I212" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J212" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="K212" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L212" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="M212" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="N212" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="O212" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="P212" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q212" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="213" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A213" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B213" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C213" s="3">
+        <v>10</v>
+      </c>
+      <c r="D213" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E213" s="3">
+        <v>10</v>
+      </c>
+      <c r="F213" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="G213" s="3">
+        <v>10</v>
+      </c>
+      <c r="H213" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I213" s="3">
+        <v>10</v>
+      </c>
+      <c r="J213" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K213" s="3">
+        <v>10</v>
+      </c>
+      <c r="L213" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M213" s="9">
+        <v>10</v>
+      </c>
+      <c r="N213" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="O213" s="9">
+        <v>10</v>
+      </c>
+      <c r="P213" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q213" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="214" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A214" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B214" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C214" s="3">
+        <v>8</v>
+      </c>
+      <c r="D214" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E214" s="3">
+        <v>8</v>
+      </c>
+      <c r="F214" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="G214" s="3">
+        <v>8</v>
+      </c>
+      <c r="H214" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I214" s="3">
+        <v>8</v>
+      </c>
+      <c r="J214" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K214" s="3">
+        <v>8</v>
+      </c>
+      <c r="L214" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M214" s="9">
+        <v>8</v>
+      </c>
+      <c r="N214" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="O214" s="9">
+        <v>8</v>
+      </c>
+      <c r="P214" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q214" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="215" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A215" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C215" s="3">
+        <v>6</v>
+      </c>
+      <c r="D215" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E215" s="3">
+        <v>8</v>
+      </c>
+      <c r="F215" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="G215" s="3">
+        <v>7</v>
+      </c>
+      <c r="H215" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I215" s="3">
+        <v>8</v>
+      </c>
+      <c r="J215" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K215" s="3">
+        <v>8</v>
+      </c>
+      <c r="L215" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M215" s="9">
+        <v>8</v>
+      </c>
+      <c r="N215" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="O215" s="9"/>
+      <c r="P215" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q215" s="9"/>
+    </row>
+    <row r="216" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A216" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B216" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C216" s="3">
+        <v>8</v>
+      </c>
+      <c r="D216" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E216" s="3">
+        <v>8</v>
+      </c>
+      <c r="F216" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="G216" s="3"/>
+      <c r="H216" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I216" s="3">
+        <v>8</v>
+      </c>
+      <c r="J216" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K216" s="3">
+        <v>6</v>
+      </c>
+      <c r="L216" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M216" s="9">
+        <v>7</v>
+      </c>
+      <c r="N216" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="O216" s="9"/>
+      <c r="P216" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q216" s="9"/>
+    </row>
+    <row r="217" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A217" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C217" s="13">
+        <v>8</v>
+      </c>
+      <c r="D217" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E217" s="13">
+        <v>8</v>
+      </c>
+      <c r="F217" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="G217" s="13">
+        <v>7</v>
+      </c>
+      <c r="H217" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I217" s="13">
+        <v>8</v>
+      </c>
+      <c r="J217" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="K217" s="13"/>
+      <c r="L217" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="M217" s="14">
+        <v>7</v>
+      </c>
+      <c r="N217" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="O217" s="14"/>
+      <c r="P217" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q217" s="14"/>
+    </row>
+    <row r="218" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A218" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B218" s="23"/>
+      <c r="C218" s="23">
+        <f>SUM(C213:C217)</f>
+        <v>40</v>
+      </c>
+      <c r="D218" s="23"/>
+      <c r="E218" s="23">
+        <f>SUM(E213:E217)</f>
+        <v>42</v>
+      </c>
+      <c r="F218" s="23"/>
+      <c r="G218" s="23">
+        <f>SUM(G213:G217)</f>
+        <v>32</v>
+      </c>
+      <c r="H218" s="23"/>
+      <c r="I218" s="23">
+        <f>SUM(I213:I217)</f>
+        <v>42</v>
+      </c>
+      <c r="J218" s="23"/>
+      <c r="K218" s="23">
+        <f>SUM(K213:K217)</f>
+        <v>32</v>
+      </c>
+      <c r="L218" s="23"/>
+      <c r="M218" s="24">
+        <f>SUM(M213:M217)</f>
+        <v>40</v>
+      </c>
+      <c r="N218" s="28"/>
+      <c r="O218" s="24">
+        <f>SUM(O213:O217)</f>
+        <v>18</v>
+      </c>
+      <c r="P218" s="28"/>
+      <c r="Q218" s="24">
+        <f>SUM(Q213:Q217)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="219" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A219" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B219" s="18"/>
+      <c r="C219" s="18">
+        <v>0</v>
+      </c>
+      <c r="D219" s="18"/>
+      <c r="E219" s="18">
+        <v>-6</v>
+      </c>
+      <c r="F219" s="18"/>
+      <c r="G219" s="18">
+        <v>-3</v>
+      </c>
+      <c r="H219" s="18"/>
+      <c r="I219" s="18">
+        <v>2</v>
+      </c>
+      <c r="J219" s="18"/>
+      <c r="K219" s="18">
+        <v>0</v>
+      </c>
+      <c r="L219" s="18"/>
+      <c r="M219" s="19">
+        <v>0</v>
+      </c>
+      <c r="N219" s="29"/>
+      <c r="O219" s="19">
+        <v>0</v>
+      </c>
+      <c r="P219" s="29"/>
+      <c r="Q219" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A220" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B220" s="21"/>
+      <c r="C220" s="21">
+        <v>3</v>
+      </c>
+      <c r="D220" s="21"/>
+      <c r="E220" s="21">
+        <v>-1</v>
+      </c>
+      <c r="F220" s="21"/>
+      <c r="G220" s="21">
+        <v>2</v>
+      </c>
+      <c r="H220" s="21"/>
+      <c r="I220" s="21">
+        <v>3</v>
+      </c>
+      <c r="J220" s="21"/>
+      <c r="K220" s="21">
+        <v>-1</v>
+      </c>
+      <c r="L220" s="21"/>
+      <c r="M220" s="22">
+        <v>1</v>
+      </c>
+      <c r="N220" s="30"/>
+      <c r="O220" s="22">
+        <v>0</v>
+      </c>
+      <c r="P220" s="30"/>
+      <c r="Q220" s="22">
+        <v>0</v>
+      </c>
+      <c r="R220" s="41"/>
+    </row>
+    <row r="221" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="222" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A222" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B222" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C222" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D222" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E222" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F222" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G222" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H222" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I222" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J222" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="K222" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L222" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="M222" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="N222" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="O222" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="P222" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q222" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="223" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A223" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B223" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C223" s="3">
+        <v>10</v>
+      </c>
+      <c r="D223" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E223" s="3">
+        <v>10</v>
+      </c>
+      <c r="F223" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G223" s="3">
+        <v>10</v>
+      </c>
+      <c r="H223" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I223" s="3">
+        <v>10</v>
+      </c>
+      <c r="J223" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K223" s="3">
+        <v>10</v>
+      </c>
+      <c r="L223" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M223" s="9">
+        <v>10</v>
+      </c>
+      <c r="N223" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="O223" s="9">
+        <v>10</v>
+      </c>
+      <c r="P223" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q223" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="224" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A224" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B224" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C224" s="3">
+        <v>8</v>
+      </c>
+      <c r="D224" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E224" s="3">
+        <v>8</v>
+      </c>
+      <c r="F224" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G224" s="3">
+        <v>8</v>
+      </c>
+      <c r="H224" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I224" s="3">
+        <v>8</v>
+      </c>
+      <c r="J224" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K224" s="3">
+        <v>8</v>
+      </c>
+      <c r="L224" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M224" s="9">
+        <v>8</v>
+      </c>
+      <c r="N224" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="O224" s="9">
+        <v>8</v>
+      </c>
+      <c r="P224" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q224" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="225" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A225" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B225" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C225" s="3">
+        <v>6</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E225" s="3">
+        <v>8</v>
+      </c>
+      <c r="F225" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G225" s="3">
+        <v>7</v>
+      </c>
+      <c r="H225" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I225" s="3">
+        <v>8</v>
+      </c>
+      <c r="J225" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K225" s="3">
+        <v>8</v>
+      </c>
+      <c r="L225" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M225" s="9">
+        <v>8</v>
+      </c>
+      <c r="N225" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="O225" s="9"/>
+      <c r="P225" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q225" s="9"/>
+    </row>
+    <row r="226" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A226" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B226" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C226" s="3">
+        <v>8</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E226" s="3">
+        <v>8</v>
+      </c>
+      <c r="F226" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G226" s="3">
+        <v>7</v>
+      </c>
+      <c r="H226" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I226" s="3">
+        <v>8</v>
+      </c>
+      <c r="J226" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K226" s="3">
+        <v>6</v>
+      </c>
+      <c r="L226" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M226" s="9">
+        <v>7</v>
+      </c>
+      <c r="N226" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="O226" s="9"/>
+      <c r="P226" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q226" s="9"/>
+    </row>
+    <row r="227" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A227" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C227" s="13">
+        <v>8</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E227" s="13">
+        <v>8</v>
+      </c>
+      <c r="F227" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G227" s="13">
+        <v>7</v>
+      </c>
+      <c r="H227" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I227" s="13">
+        <v>8</v>
+      </c>
+      <c r="J227" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="K227" s="13"/>
+      <c r="L227" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="M227" s="14">
+        <v>7</v>
+      </c>
+      <c r="N227" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="O227" s="14"/>
+      <c r="P227" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q227" s="14"/>
+    </row>
+    <row r="228" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A228" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B228" s="23"/>
+      <c r="C228" s="23">
+        <f>SUM(C223:C227)</f>
+        <v>40</v>
+      </c>
+      <c r="D228" s="23"/>
+      <c r="E228" s="23">
+        <f>SUM(E223:E227)</f>
+        <v>42</v>
+      </c>
+      <c r="F228" s="23"/>
+      <c r="G228" s="23">
+        <f>SUM(G223:G227)</f>
+        <v>39</v>
+      </c>
+      <c r="H228" s="23"/>
+      <c r="I228" s="23">
+        <f>SUM(I223:I227)</f>
+        <v>42</v>
+      </c>
+      <c r="J228" s="23"/>
+      <c r="K228" s="23">
+        <f>SUM(K223:K227)</f>
+        <v>32</v>
+      </c>
+      <c r="L228" s="23"/>
+      <c r="M228" s="24">
+        <f>SUM(M223:M227)</f>
+        <v>40</v>
+      </c>
+      <c r="N228" s="28"/>
+      <c r="O228" s="24">
+        <f>SUM(O223:O227)</f>
+        <v>18</v>
+      </c>
+      <c r="P228" s="28"/>
+      <c r="Q228" s="24">
+        <f>SUM(Q223:Q227)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="229" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A229" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B229" s="18"/>
+      <c r="C229" s="18">
+        <v>0</v>
+      </c>
+      <c r="D229" s="18"/>
+      <c r="E229" s="18">
+        <v>-6</v>
+      </c>
+      <c r="F229" s="18"/>
+      <c r="G229" s="18">
+        <v>-3</v>
+      </c>
+      <c r="H229" s="18"/>
+      <c r="I229" s="18">
+        <v>2</v>
+      </c>
+      <c r="J229" s="18"/>
+      <c r="K229" s="18">
+        <v>0</v>
+      </c>
+      <c r="L229" s="18"/>
+      <c r="M229" s="19">
+        <v>0</v>
+      </c>
+      <c r="N229" s="29"/>
+      <c r="O229" s="19">
+        <v>0</v>
+      </c>
+      <c r="P229" s="29"/>
+      <c r="Q229" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A230" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B230" s="21"/>
+      <c r="C230" s="21">
+        <v>3</v>
+      </c>
+      <c r="D230" s="21"/>
+      <c r="E230" s="21">
+        <v>-1</v>
+      </c>
+      <c r="F230" s="21"/>
+      <c r="G230" s="21">
+        <v>2</v>
+      </c>
+      <c r="H230" s="21"/>
+      <c r="I230" s="21">
+        <v>3</v>
+      </c>
+      <c r="J230" s="21"/>
+      <c r="K230" s="21">
+        <v>-1</v>
+      </c>
+      <c r="L230" s="21"/>
+      <c r="M230" s="22">
+        <v>1</v>
+      </c>
+      <c r="N230" s="30"/>
+      <c r="O230" s="22">
+        <v>0</v>
+      </c>
+      <c r="P230" s="30"/>
+      <c r="Q230" s="22">
+        <v>0</v>
+      </c>
+      <c r="R230" s="41"/>
+    </row>
+    <row r="231" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="232" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A232" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B232" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C232" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D232" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E232" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F232" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G232" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H232" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I232" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J232" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="K232" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L232" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="M232" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="N232" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="O232" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="P232" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q232" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="233" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A233" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C233" s="3">
+        <v>10</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E233" s="3">
+        <v>10</v>
+      </c>
+      <c r="F233" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G233" s="3">
+        <v>10</v>
+      </c>
+      <c r="H233" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I233" s="3">
+        <v>10</v>
+      </c>
+      <c r="J233" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K233" s="3">
+        <v>10</v>
+      </c>
+      <c r="L233" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M233" s="9">
+        <v>10</v>
+      </c>
+      <c r="N233" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="O233" s="9">
+        <v>10</v>
+      </c>
+      <c r="P233" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q233" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="234" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A234" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B234" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C234" s="3">
+        <v>8</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E234" s="3">
+        <v>8</v>
+      </c>
+      <c r="F234" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G234" s="3">
+        <v>8</v>
+      </c>
+      <c r="H234" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I234" s="3">
+        <v>8</v>
+      </c>
+      <c r="J234" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K234" s="3">
+        <v>8</v>
+      </c>
+      <c r="L234" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M234" s="9">
+        <v>8</v>
+      </c>
+      <c r="N234" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="O234" s="9">
+        <v>8</v>
+      </c>
+      <c r="P234" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q234" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="235" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A235" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B235" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C235" s="3">
+        <v>6</v>
+      </c>
+      <c r="D235" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E235" s="3">
+        <v>8</v>
+      </c>
+      <c r="F235" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G235" s="3">
+        <v>7</v>
+      </c>
+      <c r="H235" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I235" s="3">
+        <v>8</v>
+      </c>
+      <c r="J235" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K235" s="3">
+        <v>8</v>
+      </c>
+      <c r="L235" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M235" s="9">
+        <v>8</v>
+      </c>
+      <c r="N235" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="O235" s="9"/>
+      <c r="P235" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q235" s="9"/>
+    </row>
+    <row r="236" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A236" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B236" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C236" s="3">
+        <v>8</v>
+      </c>
+      <c r="D236" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E236" s="3">
+        <v>8</v>
+      </c>
+      <c r="F236" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G236" s="3"/>
+      <c r="H236" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I236" s="3">
+        <v>8</v>
+      </c>
+      <c r="J236" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K236" s="3">
+        <v>6</v>
+      </c>
+      <c r="L236" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M236" s="9">
+        <v>7</v>
+      </c>
+      <c r="N236" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="O236" s="9"/>
+      <c r="P236" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q236" s="9"/>
+    </row>
+    <row r="237" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A237" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B237" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C237" s="13">
+        <v>8</v>
+      </c>
+      <c r="D237" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E237" s="13">
+        <v>8</v>
+      </c>
+      <c r="F237" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G237" s="13">
+        <v>7</v>
+      </c>
+      <c r="H237" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I237" s="13">
+        <v>8</v>
+      </c>
+      <c r="J237" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="K237" s="13"/>
+      <c r="L237" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="M237" s="14">
+        <v>7</v>
+      </c>
+      <c r="N237" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="O237" s="14"/>
+      <c r="P237" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q237" s="14"/>
+    </row>
+    <row r="238" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A238" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B238" s="23"/>
+      <c r="C238" s="23">
+        <f>SUM(C233:C237)</f>
+        <v>40</v>
+      </c>
+      <c r="D238" s="23"/>
+      <c r="E238" s="23">
+        <f>SUM(E233:E237)</f>
+        <v>42</v>
+      </c>
+      <c r="F238" s="23"/>
+      <c r="G238" s="23">
+        <f>SUM(G233:G237)</f>
+        <v>32</v>
+      </c>
+      <c r="H238" s="23"/>
+      <c r="I238" s="23">
+        <f>SUM(I233:I237)</f>
+        <v>42</v>
+      </c>
+      <c r="J238" s="23"/>
+      <c r="K238" s="23">
+        <f>SUM(K233:K237)</f>
+        <v>32</v>
+      </c>
+      <c r="L238" s="23"/>
+      <c r="M238" s="24">
+        <f>SUM(M233:M237)</f>
+        <v>40</v>
+      </c>
+      <c r="N238" s="28"/>
+      <c r="O238" s="24">
+        <f>SUM(O233:O237)</f>
+        <v>18</v>
+      </c>
+      <c r="P238" s="28"/>
+      <c r="Q238" s="24">
+        <f>SUM(Q233:Q237)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="239" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A239" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B239" s="18"/>
+      <c r="C239" s="18">
+        <v>0</v>
+      </c>
+      <c r="D239" s="18"/>
+      <c r="E239" s="18">
+        <v>-6</v>
+      </c>
+      <c r="F239" s="18"/>
+      <c r="G239" s="18">
+        <v>-3</v>
+      </c>
+      <c r="H239" s="18"/>
+      <c r="I239" s="18">
+        <v>2</v>
+      </c>
+      <c r="J239" s="18"/>
+      <c r="K239" s="18">
+        <v>0</v>
+      </c>
+      <c r="L239" s="18"/>
+      <c r="M239" s="19">
+        <v>0</v>
+      </c>
+      <c r="N239" s="29"/>
+      <c r="O239" s="19">
+        <v>0</v>
+      </c>
+      <c r="P239" s="29"/>
+      <c r="Q239" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A240" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B240" s="21"/>
+      <c r="C240" s="21">
+        <v>3</v>
+      </c>
+      <c r="D240" s="21"/>
+      <c r="E240" s="21">
+        <v>-1</v>
+      </c>
+      <c r="F240" s="21"/>
+      <c r="G240" s="21">
+        <v>2</v>
+      </c>
+      <c r="H240" s="21"/>
+      <c r="I240" s="21">
+        <v>3</v>
+      </c>
+      <c r="J240" s="21"/>
+      <c r="K240" s="21">
+        <v>-1</v>
+      </c>
+      <c r="L240" s="21"/>
+      <c r="M240" s="22">
+        <v>1</v>
+      </c>
+      <c r="N240" s="30"/>
+      <c r="O240" s="22">
+        <v>0</v>
+      </c>
+      <c r="P240" s="30"/>
+      <c r="Q240" s="22">
+        <v>0</v>
+      </c>
+      <c r="R240" s="41"/>
+    </row>
+    <row r="241" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="242" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A242" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B242" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C242" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D242" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E242" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F242" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G242" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H242" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I242" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J242" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="K242" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L242" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="M242" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="N242" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="O242" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="P242" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q242" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="243" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A243" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B243" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C243" s="3">
+        <v>10</v>
+      </c>
+      <c r="D243" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E243" s="3">
+        <v>10</v>
+      </c>
+      <c r="F243" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G243" s="3">
+        <v>10</v>
+      </c>
+      <c r="H243" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I243" s="3">
+        <v>10</v>
+      </c>
+      <c r="J243" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K243" s="3">
+        <v>10</v>
+      </c>
+      <c r="L243" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M243" s="9">
+        <v>10</v>
+      </c>
+      <c r="N243" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="O243" s="9">
+        <v>10</v>
+      </c>
+      <c r="P243" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q243" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="244" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A244" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B244" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C244" s="3">
+        <v>8</v>
+      </c>
+      <c r="D244" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E244" s="3">
+        <v>8</v>
+      </c>
+      <c r="F244" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G244" s="3">
+        <v>8</v>
+      </c>
+      <c r="H244" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I244" s="3">
+        <v>8</v>
+      </c>
+      <c r="J244" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K244" s="3">
+        <v>8</v>
+      </c>
+      <c r="L244" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M244" s="9">
+        <v>8</v>
+      </c>
+      <c r="N244" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="O244" s="9">
+        <v>8</v>
+      </c>
+      <c r="P244" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q244" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="245" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A245" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B245" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C245" s="3">
+        <v>6</v>
+      </c>
+      <c r="D245" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E245" s="3">
+        <v>8</v>
+      </c>
+      <c r="F245" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G245" s="3">
+        <v>7</v>
+      </c>
+      <c r="H245" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I245" s="3">
+        <v>8</v>
+      </c>
+      <c r="J245" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K245" s="3">
+        <v>8</v>
+      </c>
+      <c r="L245" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M245" s="9">
+        <v>8</v>
+      </c>
+      <c r="N245" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="O245" s="9"/>
+      <c r="P245" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q245" s="9"/>
+    </row>
+    <row r="246" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A246" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B246" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C246" s="3">
+        <v>8</v>
+      </c>
+      <c r="D246" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E246" s="3">
+        <v>8</v>
+      </c>
+      <c r="F246" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G246" s="3">
+        <v>7</v>
+      </c>
+      <c r="H246" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I246" s="3">
+        <v>8</v>
+      </c>
+      <c r="J246" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K246" s="3">
+        <v>6</v>
+      </c>
+      <c r="L246" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M246" s="9">
+        <v>7</v>
+      </c>
+      <c r="N246" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="O246" s="9"/>
+      <c r="P246" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q246" s="9"/>
+    </row>
+    <row r="247" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A247" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B247" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C247" s="13">
+        <v>8</v>
+      </c>
+      <c r="D247" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E247" s="13">
+        <v>8</v>
+      </c>
+      <c r="F247" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G247" s="13">
+        <v>7</v>
+      </c>
+      <c r="H247" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I247" s="13">
+        <v>8</v>
+      </c>
+      <c r="J247" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="K247" s="13"/>
+      <c r="L247" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="M247" s="14">
+        <v>7</v>
+      </c>
+      <c r="N247" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="O247" s="14"/>
+      <c r="P247" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q247" s="14"/>
+    </row>
+    <row r="248" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A248" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B248" s="23"/>
+      <c r="C248" s="23">
+        <f>SUM(C243:C247)</f>
+        <v>40</v>
+      </c>
+      <c r="D248" s="23"/>
+      <c r="E248" s="23">
+        <f>SUM(E243:E247)</f>
+        <v>42</v>
+      </c>
+      <c r="F248" s="23"/>
+      <c r="G248" s="23">
+        <f>SUM(G243:G247)</f>
+        <v>39</v>
+      </c>
+      <c r="H248" s="23"/>
+      <c r="I248" s="23">
+        <f>SUM(I243:I247)</f>
+        <v>42</v>
+      </c>
+      <c r="J248" s="23"/>
+      <c r="K248" s="23">
+        <f>SUM(K243:K247)</f>
+        <v>32</v>
+      </c>
+      <c r="L248" s="23"/>
+      <c r="M248" s="24">
+        <f>SUM(M243:M247)</f>
+        <v>40</v>
+      </c>
+      <c r="N248" s="28"/>
+      <c r="O248" s="24">
+        <f>SUM(O243:O247)</f>
+        <v>18</v>
+      </c>
+      <c r="P248" s="28"/>
+      <c r="Q248" s="24">
+        <f>SUM(Q243:Q247)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="249" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A249" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B249" s="18"/>
+      <c r="C249" s="18">
+        <v>0</v>
+      </c>
+      <c r="D249" s="18"/>
+      <c r="E249" s="18">
+        <v>-6</v>
+      </c>
+      <c r="F249" s="18"/>
+      <c r="G249" s="18">
+        <v>-3</v>
+      </c>
+      <c r="H249" s="18"/>
+      <c r="I249" s="18">
+        <v>2</v>
+      </c>
+      <c r="J249" s="18"/>
+      <c r="K249" s="18">
+        <v>0</v>
+      </c>
+      <c r="L249" s="18"/>
+      <c r="M249" s="19">
+        <v>0</v>
+      </c>
+      <c r="N249" s="29"/>
+      <c r="O249" s="19">
+        <v>0</v>
+      </c>
+      <c r="P249" s="29"/>
+      <c r="Q249" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A250" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B250" s="21"/>
+      <c r="C250" s="21">
+        <v>3</v>
+      </c>
+      <c r="D250" s="21"/>
+      <c r="E250" s="21">
+        <v>-1</v>
+      </c>
+      <c r="F250" s="21"/>
+      <c r="G250" s="21">
+        <v>2</v>
+      </c>
+      <c r="H250" s="21"/>
+      <c r="I250" s="21">
+        <v>3</v>
+      </c>
+      <c r="J250" s="21"/>
+      <c r="K250" s="21">
+        <v>-1</v>
+      </c>
+      <c r="L250" s="21"/>
+      <c r="M250" s="22">
+        <v>1</v>
+      </c>
+      <c r="N250" s="30"/>
+      <c r="O250" s="22">
+        <v>0</v>
+      </c>
+      <c r="P250" s="30"/>
+      <c r="Q250" s="22">
+        <v>0</v>
+      </c>
+      <c r="R250" s="41"/>
+    </row>
+    <row r="251" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="252" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A252" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B252" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C252" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D252" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E252" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F252" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G252" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H252" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I252" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J252" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="K252" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L252" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="M252" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="N252" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="O252" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="P252" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q252" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="253" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A253" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B253" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C253" s="3">
+        <v>10</v>
+      </c>
+      <c r="D253" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E253" s="3">
+        <v>10</v>
+      </c>
+      <c r="F253" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G253" s="3">
+        <v>10</v>
+      </c>
+      <c r="H253" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I253" s="3">
+        <v>10</v>
+      </c>
+      <c r="J253" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K253" s="3">
+        <v>10</v>
+      </c>
+      <c r="L253" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M253" s="9">
+        <v>10</v>
+      </c>
+      <c r="N253" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="O253" s="9">
+        <v>10</v>
+      </c>
+      <c r="P253" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q253" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="254" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A254" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B254" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C254" s="3">
+        <v>8</v>
+      </c>
+      <c r="D254" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E254" s="3">
+        <v>8</v>
+      </c>
+      <c r="F254" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G254" s="3">
+        <v>8</v>
+      </c>
+      <c r="H254" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I254" s="3">
+        <v>8</v>
+      </c>
+      <c r="J254" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K254" s="3">
+        <v>8</v>
+      </c>
+      <c r="L254" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M254" s="9">
+        <v>8</v>
+      </c>
+      <c r="N254" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="O254" s="9">
+        <v>8</v>
+      </c>
+      <c r="P254" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q254" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="255" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A255" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B255" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C255" s="3">
+        <v>6</v>
+      </c>
+      <c r="D255" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E255" s="3">
+        <v>8</v>
+      </c>
+      <c r="F255" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G255" s="3">
+        <v>7</v>
+      </c>
+      <c r="H255" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I255" s="3">
+        <v>8</v>
+      </c>
+      <c r="J255" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K255" s="3">
+        <v>8</v>
+      </c>
+      <c r="L255" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M255" s="9">
+        <v>8</v>
+      </c>
+      <c r="N255" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="O255" s="9"/>
+      <c r="P255" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q255" s="9"/>
+    </row>
+    <row r="256" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A256" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B256" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C256" s="3">
+        <v>8</v>
+      </c>
+      <c r="D256" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E256" s="3">
+        <v>8</v>
+      </c>
+      <c r="F256" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G256" s="3"/>
+      <c r="H256" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I256" s="3">
+        <v>8</v>
+      </c>
+      <c r="J256" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K256" s="3">
+        <v>6</v>
+      </c>
+      <c r="L256" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M256" s="9">
+        <v>7</v>
+      </c>
+      <c r="N256" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="O256" s="9"/>
+      <c r="P256" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q256" s="9"/>
+    </row>
+    <row r="257" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A257" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B257" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C257" s="13">
+        <v>8</v>
+      </c>
+      <c r="D257" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E257" s="13">
+        <v>8</v>
+      </c>
+      <c r="F257" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G257" s="13">
+        <v>7</v>
+      </c>
+      <c r="H257" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I257" s="13">
+        <v>8</v>
+      </c>
+      <c r="J257" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="K257" s="13"/>
+      <c r="L257" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="M257" s="14">
+        <v>7</v>
+      </c>
+      <c r="N257" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="O257" s="14"/>
+      <c r="P257" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q257" s="14"/>
+    </row>
+    <row r="258" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A258" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B258" s="23"/>
+      <c r="C258" s="23">
+        <f>SUM(C253:C257)</f>
+        <v>40</v>
+      </c>
+      <c r="D258" s="23"/>
+      <c r="E258" s="23">
+        <f>SUM(E253:E257)</f>
+        <v>42</v>
+      </c>
+      <c r="F258" s="23"/>
+      <c r="G258" s="23">
+        <f>SUM(G253:G257)</f>
+        <v>32</v>
+      </c>
+      <c r="H258" s="23"/>
+      <c r="I258" s="23">
+        <f>SUM(I253:I257)</f>
+        <v>42</v>
+      </c>
+      <c r="J258" s="23"/>
+      <c r="K258" s="23">
+        <f>SUM(K253:K257)</f>
+        <v>32</v>
+      </c>
+      <c r="L258" s="23"/>
+      <c r="M258" s="24">
+        <f>SUM(M253:M257)</f>
+        <v>40</v>
+      </c>
+      <c r="N258" s="28"/>
+      <c r="O258" s="24">
+        <f>SUM(O253:O257)</f>
+        <v>18</v>
+      </c>
+      <c r="P258" s="28"/>
+      <c r="Q258" s="24">
+        <f>SUM(Q253:Q257)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="259" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A259" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B259" s="18"/>
+      <c r="C259" s="18">
+        <v>0</v>
+      </c>
+      <c r="D259" s="18"/>
+      <c r="E259" s="18">
+        <v>-6</v>
+      </c>
+      <c r="F259" s="18"/>
+      <c r="G259" s="18">
+        <v>-3</v>
+      </c>
+      <c r="H259" s="18"/>
+      <c r="I259" s="18">
+        <v>2</v>
+      </c>
+      <c r="J259" s="18"/>
+      <c r="K259" s="18">
+        <v>0</v>
+      </c>
+      <c r="L259" s="18"/>
+      <c r="M259" s="19">
+        <v>0</v>
+      </c>
+      <c r="N259" s="29"/>
+      <c r="O259" s="19">
+        <v>0</v>
+      </c>
+      <c r="P259" s="29"/>
+      <c r="Q259" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A260" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B260" s="21"/>
+      <c r="C260" s="21">
+        <v>3</v>
+      </c>
+      <c r="D260" s="21"/>
+      <c r="E260" s="21">
+        <v>-1</v>
+      </c>
+      <c r="F260" s="21"/>
+      <c r="G260" s="21">
+        <v>2</v>
+      </c>
+      <c r="H260" s="21"/>
+      <c r="I260" s="21">
+        <v>3</v>
+      </c>
+      <c r="J260" s="21"/>
+      <c r="K260" s="21">
+        <v>-1</v>
+      </c>
+      <c r="L260" s="21"/>
+      <c r="M260" s="22">
+        <v>1</v>
+      </c>
+      <c r="N260" s="30"/>
+      <c r="O260" s="22">
+        <v>0</v>
+      </c>
+      <c r="P260" s="30"/>
+      <c r="Q260" s="22">
+        <v>0</v>
+      </c>
+      <c r="R260" s="41"/>
+    </row>
+    <row r="261" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="262" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A262" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B262" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C262" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D262" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E262" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F262" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G262" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H262" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I262" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J262" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="K262" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L262" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="M262" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="N262" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="O262" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="P262" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q262" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="263" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A263" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B263" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C263" s="3">
+        <v>10</v>
+      </c>
+      <c r="D263" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E263" s="3">
+        <v>10</v>
+      </c>
+      <c r="F263" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G263" s="3">
+        <v>10</v>
+      </c>
+      <c r="H263" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I263" s="3">
+        <v>10</v>
+      </c>
+      <c r="J263" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K263" s="3">
+        <v>10</v>
+      </c>
+      <c r="L263" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M263" s="9">
+        <v>10</v>
+      </c>
+      <c r="N263" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="O263" s="9">
+        <v>10</v>
+      </c>
+      <c r="P263" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q263" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="264" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A264" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B264" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C264" s="3">
+        <v>8</v>
+      </c>
+      <c r="D264" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E264" s="3">
+        <v>8</v>
+      </c>
+      <c r="F264" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G264" s="3">
+        <v>8</v>
+      </c>
+      <c r="H264" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I264" s="3">
+        <v>8</v>
+      </c>
+      <c r="J264" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K264" s="3">
+        <v>8</v>
+      </c>
+      <c r="L264" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M264" s="9">
+        <v>8</v>
+      </c>
+      <c r="N264" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="O264" s="9">
+        <v>8</v>
+      </c>
+      <c r="P264" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q264" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="265" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A265" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B265" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C265" s="3">
+        <v>6</v>
+      </c>
+      <c r="D265" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E265" s="3">
+        <v>8</v>
+      </c>
+      <c r="F265" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G265" s="3">
+        <v>7</v>
+      </c>
+      <c r="H265" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I265" s="3">
+        <v>8</v>
+      </c>
+      <c r="J265" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K265" s="3">
+        <v>8</v>
+      </c>
+      <c r="L265" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M265" s="9">
+        <v>8</v>
+      </c>
+      <c r="N265" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="O265" s="9"/>
+      <c r="P265" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q265" s="9"/>
+    </row>
+    <row r="266" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A266" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B266" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C266" s="3">
+        <v>8</v>
+      </c>
+      <c r="D266" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E266" s="3">
+        <v>8</v>
+      </c>
+      <c r="F266" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G266" s="3">
+        <v>7</v>
+      </c>
+      <c r="H266" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I266" s="3">
+        <v>8</v>
+      </c>
+      <c r="J266" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K266" s="3">
+        <v>6</v>
+      </c>
+      <c r="L266" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M266" s="9">
+        <v>7</v>
+      </c>
+      <c r="N266" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="O266" s="9"/>
+      <c r="P266" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q266" s="9"/>
+    </row>
+    <row r="267" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A267" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B267" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C267" s="13">
+        <v>8</v>
+      </c>
+      <c r="D267" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E267" s="13">
+        <v>8</v>
+      </c>
+      <c r="F267" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G267" s="13">
+        <v>7</v>
+      </c>
+      <c r="H267" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="I267" s="13">
+        <v>8</v>
+      </c>
+      <c r="J267" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="K267" s="13"/>
+      <c r="L267" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="M267" s="14">
+        <v>7</v>
+      </c>
+      <c r="N267" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="O267" s="14"/>
+      <c r="P267" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q267" s="14"/>
+    </row>
+    <row r="268" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A268" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B268" s="23"/>
+      <c r="C268" s="23">
+        <f>SUM(C263:C267)</f>
+        <v>40</v>
+      </c>
+      <c r="D268" s="23"/>
+      <c r="E268" s="23">
+        <f>SUM(E263:E267)</f>
+        <v>42</v>
+      </c>
+      <c r="F268" s="23"/>
+      <c r="G268" s="23">
+        <f>SUM(G263:G267)</f>
+        <v>39</v>
+      </c>
+      <c r="H268" s="23"/>
+      <c r="I268" s="23">
+        <f>SUM(I263:I267)</f>
+        <v>42</v>
+      </c>
+      <c r="J268" s="23"/>
+      <c r="K268" s="23">
+        <f>SUM(K263:K267)</f>
+        <v>32</v>
+      </c>
+      <c r="L268" s="23"/>
+      <c r="M268" s="24">
+        <f>SUM(M263:M267)</f>
+        <v>40</v>
+      </c>
+      <c r="N268" s="28"/>
+      <c r="O268" s="24">
+        <f>SUM(O263:O267)</f>
+        <v>18</v>
+      </c>
+      <c r="P268" s="28"/>
+      <c r="Q268" s="24">
+        <f>SUM(Q263:Q267)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="269" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A269" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B269" s="18"/>
+      <c r="C269" s="18">
+        <v>0</v>
+      </c>
+      <c r="D269" s="18"/>
+      <c r="E269" s="18">
+        <v>-6</v>
+      </c>
+      <c r="F269" s="18"/>
+      <c r="G269" s="18">
+        <v>-3</v>
+      </c>
+      <c r="H269" s="18"/>
+      <c r="I269" s="18">
+        <v>2</v>
+      </c>
+      <c r="J269" s="18"/>
+      <c r="K269" s="18">
+        <v>0</v>
+      </c>
+      <c r="L269" s="18"/>
+      <c r="M269" s="19">
+        <v>0</v>
+      </c>
+      <c r="N269" s="29"/>
+      <c r="O269" s="19">
+        <v>0</v>
+      </c>
+      <c r="P269" s="29"/>
+      <c r="Q269" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A270" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B270" s="21"/>
+      <c r="C270" s="21">
+        <v>3</v>
+      </c>
+      <c r="D270" s="21"/>
+      <c r="E270" s="21">
+        <v>-1</v>
+      </c>
+      <c r="F270" s="21"/>
+      <c r="G270" s="21">
+        <v>2</v>
+      </c>
+      <c r="H270" s="21"/>
+      <c r="I270" s="21">
+        <v>3</v>
+      </c>
+      <c r="J270" s="21"/>
+      <c r="K270" s="21">
+        <v>-1</v>
+      </c>
+      <c r="L270" s="21"/>
+      <c r="M270" s="22">
+        <v>1</v>
+      </c>
+      <c r="N270" s="30"/>
+      <c r="O270" s="22">
+        <v>0</v>
+      </c>
+      <c r="P270" s="30"/>
+      <c r="Q270" s="22">
+        <v>0</v>
+      </c>
+      <c r="R270" s="41"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
